--- a/data/technologies_fac_simile.xlsx
+++ b/data/technologies_fac_simile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB81B7AA-0AF6-4CE5-AF4D-3A85851CE4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{936E7BA1-3017-4632-B56D-ADDC713856BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>cluster</t>
   </si>
@@ -124,6 +124,21 @@
   </si>
   <si>
     <t>CO2toEmissions</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_BE</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_DE</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_NL</t>
+  </si>
+  <si>
+    <t>H2_network_connection_in</t>
+  </si>
+  <si>
+    <t>H2_network_connection_out</t>
   </si>
 </sst>
 </file>
@@ -441,10 +456,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:AE8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -523,8 +538,23 @@
       <c r="Z1" t="s">
         <v>32</v>
       </c>
+      <c r="AA1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -603,8 +633,23 @@
       <c r="Z2">
         <v>0</v>
       </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -683,8 +728,23 @@
       <c r="Z3">
         <v>45</v>
       </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -763,8 +823,23 @@
       <c r="Z4">
         <v>39</v>
       </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -843,8 +918,23 @@
       <c r="Z5">
         <v>212</v>
       </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -923,8 +1013,23 @@
       <c r="Z6">
         <v>0</v>
       </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1003,8 +1108,23 @@
       <c r="Z7">
         <v>0</v>
       </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1081,6 +1201,21 @@
         <v>0</v>
       </c>
       <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
         <v>0</v>
       </c>
     </row>
